--- a/dane.xlsx
+++ b/dane.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\ksiz\STUDIA_DOKTORANCKIE\PRZEPIORKA\Artykuły\ZET 2026\Badania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113EF6E4-A3D4-4B1B-BB89-561B8D236B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47759780-539A-4FA1-BCD7-234418D63558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F1077B6A-ED6D-48F5-AB56-1F6DF4EDD678}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{F1077B6A-ED6D-48F5-AB56-1F6DF4EDD678}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="570">
   <si>
     <t>name</t>
   </si>
@@ -1749,6 +1749,9 @@
   </si>
   <si>
     <t>End of site</t>
+  </si>
+  <si>
+    <t>Terminal</t>
   </si>
 </sst>
 </file>
@@ -1871,13 +1874,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4647,6 +4650,9 @@
       <c r="G2" s="1" t="s">
         <v>541</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>569</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" t="s">
         <v>562</v>
@@ -4677,6 +4683,9 @@
       <c r="G3" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
       <c r="I3" s="4"/>
       <c r="K3" t="s">
         <v>542</v>
@@ -4710,6 +4719,9 @@
       <c r="G4" s="6">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>102</v>
+      </c>
       <c r="K4" t="s">
         <v>544</v>
       </c>
@@ -4742,6 +4754,9 @@
       <c r="G5" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H5">
+        <v>103</v>
+      </c>
       <c r="K5" t="s">
         <v>545</v>
       </c>
@@ -4774,6 +4789,9 @@
       <c r="G6" s="6">
         <v>0</v>
       </c>
+      <c r="H6">
+        <v>104</v>
+      </c>
       <c r="K6" t="s">
         <v>548</v>
       </c>
@@ -4806,6 +4824,9 @@
       <c r="G7" s="6">
         <v>0</v>
       </c>
+      <c r="H7">
+        <v>106</v>
+      </c>
       <c r="K7" t="s">
         <v>549</v>
       </c>
@@ -4838,6 +4859,9 @@
       <c r="G8" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H8">
+        <v>107</v>
+      </c>
       <c r="K8" t="s">
         <v>550</v>
       </c>
@@ -4870,6 +4894,9 @@
       <c r="G9" s="6">
         <v>0</v>
       </c>
+      <c r="H9">
+        <v>11</v>
+      </c>
       <c r="K9" t="s">
         <v>560</v>
       </c>
@@ -4902,6 +4929,9 @@
       <c r="G10" s="6">
         <v>0</v>
       </c>
+      <c r="H10">
+        <v>110</v>
+      </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
@@ -4928,6 +4958,9 @@
       <c r="G11" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H11">
+        <v>112</v>
+      </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
@@ -4954,6 +4987,9 @@
       <c r="G12" s="6">
         <v>0</v>
       </c>
+      <c r="H12">
+        <v>113</v>
+      </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
@@ -4980,6 +5016,9 @@
       <c r="G13" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H13">
+        <v>114</v>
+      </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
@@ -5006,6 +5045,9 @@
       <c r="G14" s="6">
         <v>0</v>
       </c>
+      <c r="H14">
+        <v>115</v>
+      </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
@@ -5032,6 +5074,9 @@
       <c r="G15" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H15">
+        <v>116</v>
+      </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
@@ -5058,6 +5103,9 @@
       <c r="G16" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H16">
+        <v>12</v>
+      </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
@@ -5084,6 +5132,9 @@
       <c r="G17" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H17">
+        <v>13</v>
+      </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
@@ -5110,6 +5161,9 @@
       <c r="G18" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H18">
+        <v>21</v>
+      </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
@@ -5136,6 +5190,9 @@
       <c r="G19" s="6">
         <v>0</v>
       </c>
+      <c r="H19">
+        <v>25</v>
+      </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
@@ -5162,6 +5219,9 @@
       <c r="G20" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H20">
+        <v>26</v>
+      </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
@@ -5188,6 +5248,9 @@
       <c r="G21" s="6">
         <v>0</v>
       </c>
+      <c r="H21">
+        <v>29</v>
+      </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
@@ -5214,6 +5277,9 @@
       <c r="G22" s="6">
         <v>0</v>
       </c>
+      <c r="H22">
+        <v>30</v>
+      </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
@@ -5240,6 +5306,9 @@
       <c r="G23" s="6">
         <v>0</v>
       </c>
+      <c r="H23">
+        <v>33</v>
+      </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
@@ -5266,6 +5335,9 @@
       <c r="G24" s="6">
         <v>0</v>
       </c>
+      <c r="H24">
+        <v>34</v>
+      </c>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
@@ -5292,6 +5364,9 @@
       <c r="G25" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H25">
+        <v>37</v>
+      </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
       <c r="P25" s="5"/>
@@ -5318,6 +5393,9 @@
       <c r="G26" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H26">
+        <v>39</v>
+      </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
@@ -5344,6 +5422,9 @@
       <c r="G27" s="6">
         <v>0</v>
       </c>
+      <c r="H27">
+        <v>40</v>
+      </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
@@ -5370,6 +5451,9 @@
       <c r="G28" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H28">
+        <v>42</v>
+      </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
@@ -5396,6 +5480,9 @@
       <c r="G29" s="6">
         <v>0</v>
       </c>
+      <c r="H29">
+        <v>45</v>
+      </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
@@ -5422,6 +5509,9 @@
       <c r="G30" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H30">
+        <v>46</v>
+      </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
@@ -5448,6 +5538,9 @@
       <c r="G31" s="6">
         <v>0</v>
       </c>
+      <c r="H31">
+        <v>47</v>
+      </c>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
@@ -5474,6 +5567,9 @@
       <c r="G32" s="6">
         <v>0</v>
       </c>
+      <c r="H32">
+        <v>49</v>
+      </c>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
@@ -5500,6 +5596,9 @@
       <c r="G33" s="6">
         <v>0</v>
       </c>
+      <c r="H33">
+        <v>5</v>
+      </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
@@ -5526,6 +5625,9 @@
       <c r="G34" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H34">
+        <v>50</v>
+      </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
@@ -5552,6 +5654,9 @@
       <c r="G35" s="6">
         <v>0</v>
       </c>
+      <c r="H35">
+        <v>52</v>
+      </c>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
@@ -5578,6 +5683,9 @@
       <c r="G36" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H36">
+        <v>54</v>
+      </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
@@ -5604,6 +5712,9 @@
       <c r="G37" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H37">
+        <v>57</v>
+      </c>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
@@ -5630,6 +5741,9 @@
       <c r="G38" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H38">
+        <v>60</v>
+      </c>
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
       <c r="P38" s="5"/>
@@ -5656,6 +5770,9 @@
       <c r="G39" s="6">
         <v>0</v>
       </c>
+      <c r="H39">
+        <v>62</v>
+      </c>
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
       <c r="P39" s="5"/>
@@ -5682,6 +5799,9 @@
       <c r="G40" s="6">
         <v>0</v>
       </c>
+      <c r="H40">
+        <v>64</v>
+      </c>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
       <c r="P40" s="5"/>
@@ -5708,6 +5828,9 @@
       <c r="G41" s="6">
         <v>0</v>
       </c>
+      <c r="H41">
+        <v>66</v>
+      </c>
       <c r="N41" s="5"/>
       <c r="O41" s="5"/>
       <c r="P41" s="5"/>
@@ -5734,6 +5857,9 @@
       <c r="G42" s="6">
         <v>0</v>
       </c>
+      <c r="H42">
+        <v>67</v>
+      </c>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
       <c r="P42" s="5"/>
@@ -5760,6 +5886,9 @@
       <c r="G43" s="6">
         <v>0</v>
       </c>
+      <c r="H43">
+        <v>7</v>
+      </c>
       <c r="N43" s="5"/>
       <c r="O43" s="5"/>
       <c r="P43" s="5"/>
@@ -5786,6 +5915,9 @@
       <c r="G44" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H44">
+        <v>72</v>
+      </c>
       <c r="N44" s="5"/>
       <c r="O44" s="5"/>
       <c r="P44" s="5"/>
@@ -5812,6 +5944,9 @@
       <c r="G45" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H45">
+        <v>73</v>
+      </c>
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
       <c r="P45" s="5"/>
@@ -5838,6 +5973,9 @@
       <c r="G46" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H46">
+        <v>75</v>
+      </c>
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
       <c r="P46" s="5"/>
@@ -5864,6 +6002,9 @@
       <c r="G47" s="6">
         <v>0</v>
       </c>
+      <c r="H47">
+        <v>76</v>
+      </c>
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
       <c r="P47" s="5"/>
@@ -5890,6 +6031,9 @@
       <c r="G48" s="6">
         <v>0</v>
       </c>
+      <c r="H48">
+        <v>77</v>
+      </c>
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
       <c r="P48" s="5"/>
@@ -5916,6 +6060,9 @@
       <c r="G49" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H49">
+        <v>80</v>
+      </c>
       <c r="N49" s="5"/>
       <c r="O49" s="5"/>
       <c r="P49" s="5"/>
@@ -5942,6 +6089,9 @@
       <c r="G50" s="6">
         <v>0</v>
       </c>
+      <c r="H50">
+        <v>81</v>
+      </c>
       <c r="N50" s="5"/>
       <c r="O50" s="5"/>
       <c r="P50" s="5"/>
@@ -5968,6 +6118,9 @@
       <c r="G51" s="6">
         <v>0</v>
       </c>
+      <c r="H51">
+        <v>83</v>
+      </c>
       <c r="N51" s="5"/>
       <c r="O51" s="5"/>
       <c r="P51" s="5"/>
@@ -5994,6 +6147,9 @@
       <c r="G52" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H52">
+        <v>87</v>
+      </c>
       <c r="N52" s="5"/>
       <c r="O52" s="5"/>
       <c r="P52" s="5"/>
@@ -6020,6 +6176,9 @@
       <c r="G53" s="6">
         <v>0</v>
       </c>
+      <c r="H53">
+        <v>88</v>
+      </c>
       <c r="N53" s="5"/>
       <c r="O53" s="5"/>
       <c r="P53" s="5"/>
@@ -6046,6 +6205,9 @@
       <c r="G54" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H54">
+        <v>93</v>
+      </c>
       <c r="N54" s="5"/>
       <c r="O54" s="5"/>
       <c r="P54" s="5"/>
@@ -6072,6 +6234,9 @@
       <c r="G55" s="6">
         <v>0</v>
       </c>
+      <c r="H55">
+        <v>95</v>
+      </c>
       <c r="N55" s="5"/>
       <c r="O55" s="5"/>
       <c r="P55" s="5"/>
@@ -6098,6 +6263,9 @@
       <c r="G56" s="6" t="s">
         <v>354</v>
       </c>
+      <c r="H56">
+        <v>96</v>
+      </c>
       <c r="N56" s="5"/>
       <c r="O56" s="5"/>
       <c r="P56" s="5"/>
@@ -6123,6 +6291,9 @@
       </c>
       <c r="G57" s="6">
         <v>0</v>
+      </c>
+      <c r="H57">
+        <v>97</v>
       </c>
       <c r="N57" s="5"/>
       <c r="O57" s="5"/>
@@ -6156,7 +6327,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="10" t="s">
         <v>554</v>
       </c>
       <c r="E1" s="1"/>
@@ -6192,7 +6363,7 @@
       <c r="C2" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D2" s="8"/>
+      <c r="D2" s="10"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" t="s">
@@ -6229,7 +6400,7 @@
       <c r="D3">
         <v>102</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>556</v>
       </c>
       <c r="H3" t="s">
@@ -6258,7 +6429,7 @@
       <c r="D4">
         <v>102</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>558</v>
       </c>
       <c r="H4" t="s">
@@ -8836,7 +9007,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="10" t="s">
         <v>554</v>
       </c>
       <c r="G1" t="s">
@@ -8856,7 +9027,7 @@
       <c r="C2" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D2" s="8"/>
+      <c r="D2" s="10"/>
       <c r="G2" t="s">
         <v>562</v>
       </c>
@@ -8877,7 +9048,7 @@
       <c r="D3">
         <v>100</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>556</v>
       </c>
       <c r="H3" t="s">
@@ -8897,7 +9068,7 @@
       <c r="D4">
         <v>100</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>558</v>
       </c>
       <c r="H4" t="s">
@@ -12668,7 +12839,7 @@
       <c r="D1" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>567</v>
       </c>
     </row>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\ksiz\STUDIA_DOKTORANCKIE\PRZEPIORKA\Artykuły\ZET 2026\Badania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24599D8-191F-46BC-AE7A-A4B6D4EF3FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA353FC-75A9-4A11-ADC6-7CD1E6DE444B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F1077B6A-ED6D-48F5-AB56-1F6DF4EDD678}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1930" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="604">
   <si>
     <t>name</t>
   </si>
@@ -1957,7 +1957,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1987,6 +1987,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -2400,7 +2401,7 @@
         <v>585</v>
       </c>
       <c r="B6">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F6" t="s">
         <v>580</v>
@@ -2411,7 +2412,7 @@
         <v>586</v>
       </c>
       <c r="B7">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6896,7 +6897,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC4B33F-E210-4AAC-9797-75DE210FFB33}">
-  <dimension ref="A1:R167"/>
+  <dimension ref="A1:R169"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="8" width="11.42578125" customWidth="1"/>
@@ -6988,8 +6989,8 @@
       <c r="A3" t="s">
         <v>250</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
+      <c r="B3" s="13">
+        <v>0</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -7023,8 +7024,8 @@
       <c r="A4" t="s">
         <v>251</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
+      <c r="B4" s="13">
+        <v>0</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -7058,8 +7059,8 @@
       <c r="A5" t="s">
         <v>252</v>
       </c>
-      <c r="B5" t="s">
-        <v>3</v>
+      <c r="B5" s="13">
+        <v>0</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
@@ -7093,8 +7094,8 @@
       <c r="A6" t="s">
         <v>253</v>
       </c>
-      <c r="B6" t="s">
-        <v>349</v>
+      <c r="B6" s="13">
+        <v>3.33</v>
       </c>
       <c r="C6" t="s">
         <v>3</v>
@@ -7122,8 +7123,8 @@
       <c r="A7" t="s">
         <v>254</v>
       </c>
-      <c r="B7" t="s">
-        <v>349</v>
+      <c r="B7" s="13">
+        <v>3.33</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
@@ -7151,8 +7152,8 @@
       <c r="A8" t="s">
         <v>255</v>
       </c>
-      <c r="B8" t="s">
-        <v>349</v>
+      <c r="B8" s="13">
+        <v>3.33</v>
       </c>
       <c r="C8" t="s">
         <v>3</v>
@@ -7180,8 +7181,8 @@
       <c r="A9" t="s">
         <v>256</v>
       </c>
-      <c r="B9" t="s">
-        <v>349</v>
+      <c r="B9" s="13">
+        <v>3.33</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
@@ -7209,8 +7210,8 @@
       <c r="A10" t="s">
         <v>257</v>
       </c>
-      <c r="B10" t="s">
-        <v>349</v>
+      <c r="B10" s="13">
+        <v>3.33</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
@@ -7238,8 +7239,8 @@
       <c r="A11" t="s">
         <v>258</v>
       </c>
-      <c r="B11" t="s">
-        <v>349</v>
+      <c r="B11" s="13">
+        <v>3.33</v>
       </c>
       <c r="C11" t="s">
         <v>3</v>
@@ -7267,8 +7268,8 @@
       <c r="A12" t="s">
         <v>259</v>
       </c>
-      <c r="B12" t="s">
-        <v>3</v>
+      <c r="B12" s="13">
+        <v>0</v>
       </c>
       <c r="C12" t="s">
         <v>3</v>
@@ -7296,8 +7297,8 @@
       <c r="A13" t="s">
         <v>260</v>
       </c>
-      <c r="B13" t="s">
-        <v>3</v>
+      <c r="B13" s="13">
+        <v>0</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
@@ -7325,8 +7326,8 @@
       <c r="A14" t="s">
         <v>261</v>
       </c>
-      <c r="B14" t="s">
-        <v>3</v>
+      <c r="B14" s="13">
+        <v>0</v>
       </c>
       <c r="C14" t="s">
         <v>3</v>
@@ -7354,8 +7355,8 @@
       <c r="A15" t="s">
         <v>262</v>
       </c>
-      <c r="B15" t="s">
-        <v>349</v>
+      <c r="B15" s="13">
+        <v>3.33</v>
       </c>
       <c r="C15" t="s">
         <v>3</v>
@@ -7383,8 +7384,8 @@
       <c r="A16" t="s">
         <v>263</v>
       </c>
-      <c r="B16" t="s">
-        <v>349</v>
+      <c r="B16" s="13">
+        <v>3.33</v>
       </c>
       <c r="C16" t="s">
         <v>3</v>
@@ -7412,8 +7413,8 @@
       <c r="A17" t="s">
         <v>264</v>
       </c>
-      <c r="B17" t="s">
-        <v>349</v>
+      <c r="B17" s="13">
+        <v>3.33</v>
       </c>
       <c r="C17" t="s">
         <v>3</v>
@@ -7441,8 +7442,8 @@
       <c r="A18" t="s">
         <v>124</v>
       </c>
-      <c r="B18" t="s">
-        <v>3</v>
+      <c r="B18" s="13">
+        <v>0</v>
       </c>
       <c r="C18" t="s">
         <v>3</v>
@@ -7470,8 +7471,8 @@
       <c r="A19" t="s">
         <v>125</v>
       </c>
-      <c r="B19" t="s">
-        <v>3</v>
+      <c r="B19" s="13">
+        <v>0</v>
       </c>
       <c r="C19" t="s">
         <v>3</v>
@@ -7499,8 +7500,8 @@
       <c r="A20" t="s">
         <v>126</v>
       </c>
-      <c r="B20" t="s">
-        <v>3</v>
+      <c r="B20" s="13">
+        <v>0</v>
       </c>
       <c r="C20" t="s">
         <v>3</v>
@@ -7528,8 +7529,8 @@
       <c r="A21" t="s">
         <v>265</v>
       </c>
-      <c r="B21" t="s">
-        <v>3</v>
+      <c r="B21" s="13">
+        <v>0</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
@@ -7557,8 +7558,8 @@
       <c r="A22" t="s">
         <v>266</v>
       </c>
-      <c r="B22" t="s">
-        <v>3</v>
+      <c r="B22" s="13">
+        <v>0</v>
       </c>
       <c r="C22" t="s">
         <v>3</v>
@@ -7586,8 +7587,8 @@
       <c r="A23" t="s">
         <v>267</v>
       </c>
-      <c r="B23" t="s">
-        <v>3</v>
+      <c r="B23" s="13">
+        <v>0</v>
       </c>
       <c r="C23" t="s">
         <v>3</v>
@@ -7615,8 +7616,8 @@
       <c r="A24" t="s">
         <v>268</v>
       </c>
-      <c r="B24" t="s">
-        <v>349</v>
+      <c r="B24" s="13">
+        <v>3.33</v>
       </c>
       <c r="C24" t="s">
         <v>3</v>
@@ -7644,8 +7645,8 @@
       <c r="A25" t="s">
         <v>269</v>
       </c>
-      <c r="B25" t="s">
-        <v>349</v>
+      <c r="B25" s="13">
+        <v>3.33</v>
       </c>
       <c r="C25" t="s">
         <v>3</v>
@@ -7673,8 +7674,8 @@
       <c r="A26" t="s">
         <v>270</v>
       </c>
-      <c r="B26" t="s">
-        <v>349</v>
+      <c r="B26" s="13">
+        <v>3.33</v>
       </c>
       <c r="C26" t="s">
         <v>3</v>
@@ -7702,8 +7703,8 @@
       <c r="A27" t="s">
         <v>271</v>
       </c>
-      <c r="B27" t="s">
-        <v>3</v>
+      <c r="B27" s="13">
+        <v>0</v>
       </c>
       <c r="C27" t="s">
         <v>3</v>
@@ -7731,8 +7732,8 @@
       <c r="A28" t="s">
         <v>272</v>
       </c>
-      <c r="B28" t="s">
-        <v>3</v>
+      <c r="B28" s="13">
+        <v>0</v>
       </c>
       <c r="C28" t="s">
         <v>3</v>
@@ -7760,8 +7761,8 @@
       <c r="A29" t="s">
         <v>273</v>
       </c>
-      <c r="B29" t="s">
-        <v>350</v>
+      <c r="B29" s="13">
+        <v>3.68</v>
       </c>
       <c r="C29" t="s">
         <v>3</v>
@@ -7789,8 +7790,8 @@
       <c r="A30" t="s">
         <v>274</v>
       </c>
-      <c r="B30" t="s">
-        <v>3</v>
+      <c r="B30" s="13">
+        <v>0</v>
       </c>
       <c r="C30" t="s">
         <v>3</v>
@@ -7818,8 +7819,8 @@
       <c r="A31" t="s">
         <v>275</v>
       </c>
-      <c r="B31" t="s">
-        <v>3</v>
+      <c r="B31" s="13">
+        <v>0</v>
       </c>
       <c r="C31" t="s">
         <v>3</v>
@@ -7847,8 +7848,8 @@
       <c r="A32" t="s">
         <v>276</v>
       </c>
-      <c r="B32" t="s">
-        <v>3</v>
+      <c r="B32" s="13">
+        <v>0</v>
       </c>
       <c r="C32" t="s">
         <v>3</v>
@@ -7867,8 +7868,8 @@
       <c r="A33" t="s">
         <v>277</v>
       </c>
-      <c r="B33" t="s">
-        <v>349</v>
+      <c r="B33" s="13">
+        <v>3.33</v>
       </c>
       <c r="C33" t="s">
         <v>3</v>
@@ -7887,8 +7888,8 @@
       <c r="A34" t="s">
         <v>278</v>
       </c>
-      <c r="B34" t="s">
-        <v>349</v>
+      <c r="B34" s="13">
+        <v>3.33</v>
       </c>
       <c r="C34" t="s">
         <v>3</v>
@@ -7907,8 +7908,8 @@
       <c r="A35" t="s">
         <v>279</v>
       </c>
-      <c r="B35" t="s">
-        <v>349</v>
+      <c r="B35" s="13">
+        <v>3.33</v>
       </c>
       <c r="C35" t="s">
         <v>3</v>
@@ -7927,8 +7928,8 @@
       <c r="A36" t="s">
         <v>280</v>
       </c>
-      <c r="B36" t="s">
-        <v>3</v>
+      <c r="B36" s="13">
+        <v>0</v>
       </c>
       <c r="C36" t="s">
         <v>3</v>
@@ -7947,8 +7948,8 @@
       <c r="A37" t="s">
         <v>281</v>
       </c>
-      <c r="B37" t="s">
-        <v>3</v>
+      <c r="B37" s="13">
+        <v>0</v>
       </c>
       <c r="C37" t="s">
         <v>3</v>
@@ -7967,8 +7968,8 @@
       <c r="A38" t="s">
         <v>282</v>
       </c>
-      <c r="B38" t="s">
-        <v>3</v>
+      <c r="B38" s="13">
+        <v>0</v>
       </c>
       <c r="C38" t="s">
         <v>3</v>
@@ -7987,8 +7988,8 @@
       <c r="A39" t="s">
         <v>127</v>
       </c>
-      <c r="B39" t="s">
-        <v>3</v>
+      <c r="B39" s="13">
+        <v>0</v>
       </c>
       <c r="C39" t="s">
         <v>3</v>
@@ -8007,8 +8008,8 @@
       <c r="A40" t="s">
         <v>128</v>
       </c>
-      <c r="B40" t="s">
-        <v>3</v>
+      <c r="B40" s="13">
+        <v>0</v>
       </c>
       <c r="C40" t="s">
         <v>3</v>
@@ -8027,8 +8028,8 @@
       <c r="A41" t="s">
         <v>129</v>
       </c>
-      <c r="B41" t="s">
-        <v>3</v>
+      <c r="B41" s="13">
+        <v>0</v>
       </c>
       <c r="C41" t="s">
         <v>3</v>
@@ -8047,8 +8048,8 @@
       <c r="A42" t="s">
         <v>130</v>
       </c>
-      <c r="B42" t="s">
-        <v>3</v>
+      <c r="B42" s="13">
+        <v>0</v>
       </c>
       <c r="C42" t="s">
         <v>3</v>
@@ -8067,8 +8068,8 @@
       <c r="A43" t="s">
         <v>131</v>
       </c>
-      <c r="B43" t="s">
-        <v>3</v>
+      <c r="B43" s="13">
+        <v>0</v>
       </c>
       <c r="C43" t="s">
         <v>3</v>
@@ -8087,8 +8088,8 @@
       <c r="A44" t="s">
         <v>132</v>
       </c>
-      <c r="B44" t="s">
-        <v>3</v>
+      <c r="B44" s="13">
+        <v>0</v>
       </c>
       <c r="C44" t="s">
         <v>3</v>
@@ -8107,8 +8108,8 @@
       <c r="A45" t="s">
         <v>133</v>
       </c>
-      <c r="B45" t="s">
-        <v>349</v>
+      <c r="B45" s="13">
+        <v>3.33</v>
       </c>
       <c r="C45" t="s">
         <v>3</v>
@@ -8127,8 +8128,8 @@
       <c r="A46" t="s">
         <v>134</v>
       </c>
-      <c r="B46" t="s">
-        <v>349</v>
+      <c r="B46" s="13">
+        <v>3.33</v>
       </c>
       <c r="C46" t="s">
         <v>3</v>
@@ -8147,8 +8148,8 @@
       <c r="A47" t="s">
         <v>135</v>
       </c>
-      <c r="B47" t="s">
-        <v>349</v>
+      <c r="B47" s="13">
+        <v>3.33</v>
       </c>
       <c r="C47" t="s">
         <v>3</v>
@@ -8167,8 +8168,8 @@
       <c r="A48" t="s">
         <v>136</v>
       </c>
-      <c r="B48" t="s">
-        <v>3</v>
+      <c r="B48" s="13">
+        <v>0</v>
       </c>
       <c r="C48" t="s">
         <v>3</v>
@@ -8187,8 +8188,8 @@
       <c r="A49" t="s">
         <v>137</v>
       </c>
-      <c r="B49" t="s">
-        <v>3</v>
+      <c r="B49" s="13">
+        <v>0</v>
       </c>
       <c r="C49" t="s">
         <v>3</v>
@@ -8207,8 +8208,8 @@
       <c r="A50" t="s">
         <v>138</v>
       </c>
-      <c r="B50" t="s">
-        <v>350</v>
+      <c r="B50" s="13">
+        <v>3.68</v>
       </c>
       <c r="C50" t="s">
         <v>3</v>
@@ -8227,8 +8228,8 @@
       <c r="A51" t="s">
         <v>139</v>
       </c>
-      <c r="B51" t="s">
-        <v>3</v>
+      <c r="B51" s="13">
+        <v>0</v>
       </c>
       <c r="C51" t="s">
         <v>3</v>
@@ -8247,8 +8248,8 @@
       <c r="A52" t="s">
         <v>140</v>
       </c>
-      <c r="B52" t="s">
-        <v>3</v>
+      <c r="B52" s="13">
+        <v>0</v>
       </c>
       <c r="C52" t="s">
         <v>3</v>
@@ -8267,8 +8268,8 @@
       <c r="A53" t="s">
         <v>141</v>
       </c>
-      <c r="B53" t="s">
-        <v>3</v>
+      <c r="B53" s="13">
+        <v>0</v>
       </c>
       <c r="C53" t="s">
         <v>3</v>
@@ -8287,8 +8288,8 @@
       <c r="A54" t="s">
         <v>142</v>
       </c>
-      <c r="B54" t="s">
-        <v>349</v>
+      <c r="B54" s="13">
+        <v>3.33</v>
       </c>
       <c r="C54" t="s">
         <v>3</v>
@@ -8307,8 +8308,8 @@
       <c r="A55" t="s">
         <v>143</v>
       </c>
-      <c r="B55" t="s">
-        <v>349</v>
+      <c r="B55" s="13">
+        <v>3.33</v>
       </c>
       <c r="C55" t="s">
         <v>3</v>
@@ -8327,8 +8328,8 @@
       <c r="A56" t="s">
         <v>144</v>
       </c>
-      <c r="B56" t="s">
-        <v>349</v>
+      <c r="B56" s="13">
+        <v>3.33</v>
       </c>
       <c r="C56" t="s">
         <v>3</v>
@@ -8347,8 +8348,8 @@
       <c r="A57" t="s">
         <v>145</v>
       </c>
-      <c r="B57" t="s">
-        <v>3</v>
+      <c r="B57" s="13">
+        <v>0</v>
       </c>
       <c r="C57" t="s">
         <v>3</v>
@@ -8367,8 +8368,8 @@
       <c r="A58" t="s">
         <v>146</v>
       </c>
-      <c r="B58" t="s">
-        <v>3</v>
+      <c r="B58" s="13">
+        <v>0</v>
       </c>
       <c r="C58" t="s">
         <v>3</v>
@@ -8387,8 +8388,8 @@
       <c r="A59" t="s">
         <v>147</v>
       </c>
-      <c r="B59" t="s">
-        <v>3</v>
+      <c r="B59" s="13">
+        <v>0</v>
       </c>
       <c r="C59" t="s">
         <v>3</v>
@@ -8407,8 +8408,8 @@
       <c r="A60" t="s">
         <v>148</v>
       </c>
-      <c r="B60" t="s">
-        <v>3</v>
+      <c r="B60" s="13">
+        <v>0</v>
       </c>
       <c r="C60" t="s">
         <v>3</v>
@@ -8427,8 +8428,8 @@
       <c r="A61" t="s">
         <v>149</v>
       </c>
-      <c r="B61" t="s">
-        <v>3</v>
+      <c r="B61" s="13">
+        <v>0</v>
       </c>
       <c r="C61" t="s">
         <v>3</v>
@@ -8447,8 +8448,8 @@
       <c r="A62" t="s">
         <v>150</v>
       </c>
-      <c r="B62" t="s">
-        <v>3</v>
+      <c r="B62" s="13">
+        <v>0</v>
       </c>
       <c r="C62" t="s">
         <v>3</v>
@@ -8467,8 +8468,8 @@
       <c r="A63" t="s">
         <v>151</v>
       </c>
-      <c r="B63" t="s">
-        <v>349</v>
+      <c r="B63" s="13">
+        <v>3.33</v>
       </c>
       <c r="C63" t="s">
         <v>3</v>
@@ -8487,8 +8488,8 @@
       <c r="A64" t="s">
         <v>152</v>
       </c>
-      <c r="B64" t="s">
-        <v>349</v>
+      <c r="B64" s="13">
+        <v>3.33</v>
       </c>
       <c r="C64" t="s">
         <v>3</v>
@@ -8507,8 +8508,8 @@
       <c r="A65" t="s">
         <v>153</v>
       </c>
-      <c r="B65" t="s">
-        <v>349</v>
+      <c r="B65" s="13">
+        <v>3.33</v>
       </c>
       <c r="C65" t="s">
         <v>3</v>
@@ -8527,8 +8528,8 @@
       <c r="A66" t="s">
         <v>154</v>
       </c>
-      <c r="B66" t="s">
-        <v>3</v>
+      <c r="B66" s="13">
+        <v>0</v>
       </c>
       <c r="C66" t="s">
         <v>3</v>
@@ -8547,8 +8548,8 @@
       <c r="A67" t="s">
         <v>155</v>
       </c>
-      <c r="B67" t="s">
-        <v>3</v>
+      <c r="B67" s="13">
+        <v>0</v>
       </c>
       <c r="C67" t="s">
         <v>3</v>
@@ -8567,8 +8568,8 @@
       <c r="A68" t="s">
         <v>156</v>
       </c>
-      <c r="B68" t="s">
-        <v>3</v>
+      <c r="B68" s="13">
+        <v>0</v>
       </c>
       <c r="C68" t="s">
         <v>3</v>
@@ -8587,8 +8588,8 @@
       <c r="A69" t="s">
         <v>157</v>
       </c>
-      <c r="B69" t="s">
-        <v>349</v>
+      <c r="B69" s="13">
+        <v>3.33</v>
       </c>
       <c r="C69" t="s">
         <v>3</v>
@@ -8607,8 +8608,8 @@
       <c r="A70" t="s">
         <v>158</v>
       </c>
-      <c r="B70" t="s">
-        <v>349</v>
+      <c r="B70" s="13">
+        <v>3.33</v>
       </c>
       <c r="C70" t="s">
         <v>3</v>
@@ -8627,8 +8628,8 @@
       <c r="A71" t="s">
         <v>159</v>
       </c>
-      <c r="B71" t="s">
-        <v>349</v>
+      <c r="B71" s="13">
+        <v>3.33</v>
       </c>
       <c r="C71" t="s">
         <v>3</v>
@@ -8647,8 +8648,8 @@
       <c r="A72" t="s">
         <v>160</v>
       </c>
-      <c r="B72" t="s">
-        <v>3</v>
+      <c r="B72" s="13">
+        <v>0</v>
       </c>
       <c r="C72" t="s">
         <v>3</v>
@@ -8667,8 +8668,8 @@
       <c r="A73" t="s">
         <v>161</v>
       </c>
-      <c r="B73" t="s">
-        <v>3</v>
+      <c r="B73" s="13">
+        <v>0</v>
       </c>
       <c r="C73" t="s">
         <v>3</v>
@@ -8687,8 +8688,8 @@
       <c r="A74" t="s">
         <v>162</v>
       </c>
-      <c r="B74" t="s">
-        <v>3</v>
+      <c r="B74" s="13">
+        <v>0</v>
       </c>
       <c r="C74" t="s">
         <v>3</v>
@@ -8707,8 +8708,8 @@
       <c r="A75" t="s">
         <v>163</v>
       </c>
-      <c r="B75" t="s">
-        <v>349</v>
+      <c r="B75" s="13">
+        <v>3.33</v>
       </c>
       <c r="C75" t="s">
         <v>3</v>
@@ -8727,8 +8728,8 @@
       <c r="A76" t="s">
         <v>164</v>
       </c>
-      <c r="B76" t="s">
-        <v>349</v>
+      <c r="B76" s="13">
+        <v>3.33</v>
       </c>
       <c r="C76" t="s">
         <v>3</v>
@@ -8747,8 +8748,8 @@
       <c r="A77" t="s">
         <v>165</v>
       </c>
-      <c r="B77" t="s">
-        <v>349</v>
+      <c r="B77" s="13">
+        <v>3.33</v>
       </c>
       <c r="C77" t="s">
         <v>3</v>
@@ -8767,8 +8768,8 @@
       <c r="A78" t="s">
         <v>166</v>
       </c>
-      <c r="B78" t="s">
-        <v>3</v>
+      <c r="B78" s="13">
+        <v>0</v>
       </c>
       <c r="C78" t="s">
         <v>3</v>
@@ -8787,8 +8788,8 @@
       <c r="A79" t="s">
         <v>167</v>
       </c>
-      <c r="B79" t="s">
-        <v>3</v>
+      <c r="B79" s="13">
+        <v>0</v>
       </c>
       <c r="C79" t="s">
         <v>3</v>
@@ -8807,8 +8808,8 @@
       <c r="A80" t="s">
         <v>168</v>
       </c>
-      <c r="B80" t="s">
-        <v>3</v>
+      <c r="B80" s="13">
+        <v>0</v>
       </c>
       <c r="C80" t="s">
         <v>3</v>
@@ -8827,8 +8828,8 @@
       <c r="A81" t="s">
         <v>169</v>
       </c>
-      <c r="B81" t="s">
-        <v>3</v>
+      <c r="B81" s="13">
+        <v>0</v>
       </c>
       <c r="C81" t="s">
         <v>3</v>
@@ -8847,8 +8848,8 @@
       <c r="A82" t="s">
         <v>170</v>
       </c>
-      <c r="B82" t="s">
-        <v>3</v>
+      <c r="B82" s="13">
+        <v>0</v>
       </c>
       <c r="C82" t="s">
         <v>3</v>
@@ -8867,8 +8868,8 @@
       <c r="A83" t="s">
         <v>171</v>
       </c>
-      <c r="B83" t="s">
-        <v>3</v>
+      <c r="B83" s="13">
+        <v>0</v>
       </c>
       <c r="C83" t="s">
         <v>3</v>
@@ -8887,8 +8888,8 @@
       <c r="A84" t="s">
         <v>172</v>
       </c>
-      <c r="B84" t="s">
-        <v>349</v>
+      <c r="B84" s="13">
+        <v>3.33</v>
       </c>
       <c r="C84" t="s">
         <v>3</v>
@@ -8907,8 +8908,8 @@
       <c r="A85" t="s">
         <v>173</v>
       </c>
-      <c r="B85" t="s">
-        <v>349</v>
+      <c r="B85" s="13">
+        <v>3.33</v>
       </c>
       <c r="C85" t="s">
         <v>3</v>
@@ -8927,8 +8928,8 @@
       <c r="A86" t="s">
         <v>174</v>
       </c>
-      <c r="B86" t="s">
-        <v>349</v>
+      <c r="B86" s="13">
+        <v>3.33</v>
       </c>
       <c r="C86" t="s">
         <v>3</v>
@@ -8947,8 +8948,8 @@
       <c r="A87" t="s">
         <v>175</v>
       </c>
-      <c r="B87" t="s">
-        <v>3</v>
+      <c r="B87" s="13">
+        <v>0</v>
       </c>
       <c r="C87" t="s">
         <v>3</v>
@@ -8967,8 +8968,8 @@
       <c r="A88" t="s">
         <v>176</v>
       </c>
-      <c r="B88" t="s">
-        <v>3</v>
+      <c r="B88" s="13">
+        <v>0</v>
       </c>
       <c r="C88" t="s">
         <v>3</v>
@@ -8987,8 +8988,8 @@
       <c r="A89" t="s">
         <v>177</v>
       </c>
-      <c r="B89" t="s">
-        <v>3</v>
+      <c r="B89" s="13">
+        <v>0</v>
       </c>
       <c r="C89" t="s">
         <v>3</v>
@@ -9007,8 +9008,8 @@
       <c r="A90" t="s">
         <v>178</v>
       </c>
-      <c r="B90" t="s">
-        <v>349</v>
+      <c r="B90" s="13">
+        <v>3.33</v>
       </c>
       <c r="C90" t="s">
         <v>3</v>
@@ -9027,8 +9028,8 @@
       <c r="A91" t="s">
         <v>179</v>
       </c>
-      <c r="B91" t="s">
-        <v>349</v>
+      <c r="B91" s="13">
+        <v>3.33</v>
       </c>
       <c r="C91" t="s">
         <v>3</v>
@@ -9047,8 +9048,8 @@
       <c r="A92" t="s">
         <v>180</v>
       </c>
-      <c r="B92" t="s">
-        <v>349</v>
+      <c r="B92" s="13">
+        <v>3.33</v>
       </c>
       <c r="C92" t="s">
         <v>3</v>
@@ -9067,8 +9068,8 @@
       <c r="A93" t="s">
         <v>181</v>
       </c>
-      <c r="B93" t="s">
-        <v>3</v>
+      <c r="B93" s="13">
+        <v>0</v>
       </c>
       <c r="C93" t="s">
         <v>3</v>
@@ -9087,8 +9088,8 @@
       <c r="A94" t="s">
         <v>182</v>
       </c>
-      <c r="B94" t="s">
-        <v>3</v>
+      <c r="B94" s="13">
+        <v>0</v>
       </c>
       <c r="C94" t="s">
         <v>3</v>
@@ -9107,8 +9108,8 @@
       <c r="A95" t="s">
         <v>183</v>
       </c>
-      <c r="B95" t="s">
-        <v>350</v>
+      <c r="B95" s="13">
+        <v>3.68</v>
       </c>
       <c r="C95" t="s">
         <v>3</v>
@@ -9127,8 +9128,8 @@
       <c r="A96" t="s">
         <v>184</v>
       </c>
-      <c r="B96" t="s">
-        <v>3</v>
+      <c r="B96" s="13">
+        <v>0</v>
       </c>
       <c r="C96" t="s">
         <v>3</v>
@@ -9147,8 +9148,8 @@
       <c r="A97" t="s">
         <v>185</v>
       </c>
-      <c r="B97" t="s">
-        <v>3</v>
+      <c r="B97" s="13">
+        <v>0</v>
       </c>
       <c r="C97" t="s">
         <v>3</v>
@@ -9167,8 +9168,8 @@
       <c r="A98" t="s">
         <v>186</v>
       </c>
-      <c r="B98" t="s">
-        <v>3</v>
+      <c r="B98" s="13">
+        <v>0</v>
       </c>
       <c r="C98" t="s">
         <v>3</v>
@@ -9187,8 +9188,8 @@
       <c r="A99" t="s">
         <v>187</v>
       </c>
-      <c r="B99" t="s">
-        <v>349</v>
+      <c r="B99" s="13">
+        <v>3.33</v>
       </c>
       <c r="C99" t="s">
         <v>3</v>
@@ -9207,8 +9208,8 @@
       <c r="A100" t="s">
         <v>188</v>
       </c>
-      <c r="B100" t="s">
-        <v>349</v>
+      <c r="B100" s="13">
+        <v>3.33</v>
       </c>
       <c r="C100" t="s">
         <v>3</v>
@@ -9227,8 +9228,8 @@
       <c r="A101" t="s">
         <v>189</v>
       </c>
-      <c r="B101" t="s">
-        <v>349</v>
+      <c r="B101" s="13">
+        <v>3.33</v>
       </c>
       <c r="C101" t="s">
         <v>3</v>
@@ -9247,8 +9248,8 @@
       <c r="A102" t="s">
         <v>190</v>
       </c>
-      <c r="B102" t="s">
-        <v>3</v>
+      <c r="B102" s="13">
+        <v>0</v>
       </c>
       <c r="C102" t="s">
         <v>3</v>
@@ -9267,8 +9268,8 @@
       <c r="A103" t="s">
         <v>191</v>
       </c>
-      <c r="B103" t="s">
-        <v>3</v>
+      <c r="B103" s="13">
+        <v>0</v>
       </c>
       <c r="C103" t="s">
         <v>3</v>
@@ -9287,8 +9288,8 @@
       <c r="A104" t="s">
         <v>192</v>
       </c>
-      <c r="B104" t="s">
-        <v>3</v>
+      <c r="B104" s="13">
+        <v>0</v>
       </c>
       <c r="C104" t="s">
         <v>3</v>
@@ -9307,8 +9308,8 @@
       <c r="A105" t="s">
         <v>118</v>
       </c>
-      <c r="B105" t="s">
-        <v>349</v>
+      <c r="B105" s="13">
+        <v>3.33</v>
       </c>
       <c r="C105" t="s">
         <v>3</v>
@@ -9327,8 +9328,8 @@
       <c r="A106" t="s">
         <v>119</v>
       </c>
-      <c r="B106" t="s">
-        <v>349</v>
+      <c r="B106" s="13">
+        <v>3.33</v>
       </c>
       <c r="C106" t="s">
         <v>3</v>
@@ -9347,8 +9348,8 @@
       <c r="A107" t="s">
         <v>120</v>
       </c>
-      <c r="B107" t="s">
-        <v>349</v>
+      <c r="B107" s="13">
+        <v>3.33</v>
       </c>
       <c r="C107" t="s">
         <v>3</v>
@@ -9367,8 +9368,8 @@
       <c r="A108" t="s">
         <v>193</v>
       </c>
-      <c r="B108" t="s">
-        <v>349</v>
+      <c r="B108" s="13">
+        <v>3.33</v>
       </c>
       <c r="C108" t="s">
         <v>3</v>
@@ -9387,8 +9388,8 @@
       <c r="A109" t="s">
         <v>194</v>
       </c>
-      <c r="B109" t="s">
-        <v>349</v>
+      <c r="B109" s="13">
+        <v>3.33</v>
       </c>
       <c r="C109" t="s">
         <v>3</v>
@@ -9407,8 +9408,8 @@
       <c r="A110" t="s">
         <v>195</v>
       </c>
-      <c r="B110" t="s">
-        <v>349</v>
+      <c r="B110" s="13">
+        <v>3.33</v>
       </c>
       <c r="C110" t="s">
         <v>3</v>
@@ -9427,8 +9428,8 @@
       <c r="A111" t="s">
         <v>196</v>
       </c>
-      <c r="B111" t="s">
-        <v>349</v>
+      <c r="B111" s="13">
+        <v>3.33</v>
       </c>
       <c r="C111" t="s">
         <v>3</v>
@@ -9447,8 +9448,8 @@
       <c r="A112" t="s">
         <v>197</v>
       </c>
-      <c r="B112" t="s">
-        <v>349</v>
+      <c r="B112" s="13">
+        <v>3.33</v>
       </c>
       <c r="C112" t="s">
         <v>3</v>
@@ -9467,8 +9468,8 @@
       <c r="A113" t="s">
         <v>198</v>
       </c>
-      <c r="B113" t="s">
-        <v>349</v>
+      <c r="B113" s="13">
+        <v>3.33</v>
       </c>
       <c r="C113" t="s">
         <v>3</v>
@@ -9487,8 +9488,8 @@
       <c r="A114" t="s">
         <v>199</v>
       </c>
-      <c r="B114" t="s">
-        <v>3</v>
+      <c r="B114" s="13">
+        <v>0</v>
       </c>
       <c r="C114" t="s">
         <v>3</v>
@@ -9507,8 +9508,8 @@
       <c r="A115" t="s">
         <v>200</v>
       </c>
-      <c r="B115" t="s">
-        <v>3</v>
+      <c r="B115" s="13">
+        <v>0</v>
       </c>
       <c r="C115" t="s">
         <v>3</v>
@@ -9527,8 +9528,8 @@
       <c r="A116" t="s">
         <v>201</v>
       </c>
-      <c r="B116" t="s">
-        <v>3</v>
+      <c r="B116" s="13">
+        <v>0</v>
       </c>
       <c r="C116" t="s">
         <v>3</v>
@@ -9547,8 +9548,8 @@
       <c r="A117" t="s">
         <v>202</v>
       </c>
-      <c r="B117" t="s">
-        <v>349</v>
+      <c r="B117" s="13">
+        <v>3.33</v>
       </c>
       <c r="C117" t="s">
         <v>3</v>
@@ -9567,8 +9568,8 @@
       <c r="A118" t="s">
         <v>203</v>
       </c>
-      <c r="B118" t="s">
-        <v>349</v>
+      <c r="B118" s="13">
+        <v>3.33</v>
       </c>
       <c r="C118" t="s">
         <v>3</v>
@@ -9587,8 +9588,8 @@
       <c r="A119" t="s">
         <v>204</v>
       </c>
-      <c r="B119" t="s">
-        <v>349</v>
+      <c r="B119" s="13">
+        <v>3.33</v>
       </c>
       <c r="C119" t="s">
         <v>3</v>
@@ -9607,8 +9608,8 @@
       <c r="A120" t="s">
         <v>205</v>
       </c>
-      <c r="B120" t="s">
-        <v>3</v>
+      <c r="B120" s="13">
+        <v>0</v>
       </c>
       <c r="C120" t="s">
         <v>3</v>
@@ -9627,8 +9628,8 @@
       <c r="A121" t="s">
         <v>206</v>
       </c>
-      <c r="B121" t="s">
-        <v>3</v>
+      <c r="B121" s="13">
+        <v>0</v>
       </c>
       <c r="C121" t="s">
         <v>3</v>
@@ -9647,8 +9648,8 @@
       <c r="A122" t="s">
         <v>207</v>
       </c>
-      <c r="B122" t="s">
-        <v>3</v>
+      <c r="B122" s="13">
+        <v>0</v>
       </c>
       <c r="C122" t="s">
         <v>3</v>
@@ -9667,8 +9668,8 @@
       <c r="A123" t="s">
         <v>208</v>
       </c>
-      <c r="B123" t="s">
-        <v>349</v>
+      <c r="B123" s="13">
+        <v>3.33</v>
       </c>
       <c r="C123" t="s">
         <v>3</v>
@@ -9687,8 +9688,8 @@
       <c r="A124" t="s">
         <v>209</v>
       </c>
-      <c r="B124" t="s">
-        <v>349</v>
+      <c r="B124" s="13">
+        <v>3.33</v>
       </c>
       <c r="C124" t="s">
         <v>3</v>
@@ -9707,8 +9708,8 @@
       <c r="A125" t="s">
         <v>210</v>
       </c>
-      <c r="B125" t="s">
-        <v>349</v>
+      <c r="B125" s="13">
+        <v>3.33</v>
       </c>
       <c r="C125" t="s">
         <v>3</v>
@@ -9727,8 +9728,8 @@
       <c r="A126" t="s">
         <v>211</v>
       </c>
-      <c r="B126" t="s">
-        <v>3</v>
+      <c r="B126" s="13">
+        <v>0</v>
       </c>
       <c r="C126" t="s">
         <v>3</v>
@@ -9747,8 +9748,8 @@
       <c r="A127" t="s">
         <v>212</v>
       </c>
-      <c r="B127" t="s">
-        <v>3</v>
+      <c r="B127" s="13">
+        <v>0</v>
       </c>
       <c r="C127" t="s">
         <v>3</v>
@@ -9767,8 +9768,8 @@
       <c r="A128" t="s">
         <v>213</v>
       </c>
-      <c r="B128" t="s">
-        <v>350</v>
+      <c r="B128" s="13">
+        <v>3.68</v>
       </c>
       <c r="C128" t="s">
         <v>3</v>
@@ -9787,8 +9788,8 @@
       <c r="A129" t="s">
         <v>214</v>
       </c>
-      <c r="B129" t="s">
-        <v>3</v>
+      <c r="B129" s="13">
+        <v>0</v>
       </c>
       <c r="C129" t="s">
         <v>3</v>
@@ -9807,8 +9808,8 @@
       <c r="A130" t="s">
         <v>215</v>
       </c>
-      <c r="B130" t="s">
-        <v>3</v>
+      <c r="B130" s="13">
+        <v>0</v>
       </c>
       <c r="C130" t="s">
         <v>3</v>
@@ -9827,8 +9828,8 @@
       <c r="A131" t="s">
         <v>216</v>
       </c>
-      <c r="B131" t="s">
-        <v>3</v>
+      <c r="B131" s="13">
+        <v>0</v>
       </c>
       <c r="C131" t="s">
         <v>3</v>
@@ -9847,8 +9848,8 @@
       <c r="A132" t="s">
         <v>217</v>
       </c>
-      <c r="B132" t="s">
-        <v>349</v>
+      <c r="B132" s="13">
+        <v>3.33</v>
       </c>
       <c r="C132" t="s">
         <v>3</v>
@@ -9867,8 +9868,8 @@
       <c r="A133" t="s">
         <v>218</v>
       </c>
-      <c r="B133" t="s">
-        <v>349</v>
+      <c r="B133" s="13">
+        <v>3.33</v>
       </c>
       <c r="C133" t="s">
         <v>3</v>
@@ -9887,8 +9888,8 @@
       <c r="A134" t="s">
         <v>219</v>
       </c>
-      <c r="B134" t="s">
-        <v>349</v>
+      <c r="B134" s="13">
+        <v>3.33</v>
       </c>
       <c r="C134" t="s">
         <v>3</v>
@@ -9907,8 +9908,8 @@
       <c r="A135" t="s">
         <v>220</v>
       </c>
-      <c r="B135" t="s">
-        <v>3</v>
+      <c r="B135" s="13">
+        <v>0</v>
       </c>
       <c r="C135" t="s">
         <v>3</v>
@@ -9927,8 +9928,8 @@
       <c r="A136" t="s">
         <v>221</v>
       </c>
-      <c r="B136" t="s">
-        <v>3</v>
+      <c r="B136" s="13">
+        <v>0</v>
       </c>
       <c r="C136" t="s">
         <v>3</v>
@@ -9947,8 +9948,8 @@
       <c r="A137" t="s">
         <v>222</v>
       </c>
-      <c r="B137" t="s">
-        <v>3</v>
+      <c r="B137" s="13">
+        <v>0</v>
       </c>
       <c r="C137" t="s">
         <v>3</v>
@@ -9967,8 +9968,8 @@
       <c r="A138" t="s">
         <v>121</v>
       </c>
-      <c r="B138" t="s">
-        <v>349</v>
+      <c r="B138" s="13">
+        <v>3.33</v>
       </c>
       <c r="C138" t="s">
         <v>3</v>
@@ -9987,8 +9988,8 @@
       <c r="A139" t="s">
         <v>122</v>
       </c>
-      <c r="B139" t="s">
-        <v>349</v>
+      <c r="B139" s="13">
+        <v>3.33</v>
       </c>
       <c r="C139" t="s">
         <v>3</v>
@@ -10007,8 +10008,8 @@
       <c r="A140" t="s">
         <v>123</v>
       </c>
-      <c r="B140" t="s">
-        <v>349</v>
+      <c r="B140" s="13">
+        <v>3.33</v>
       </c>
       <c r="C140" t="s">
         <v>3</v>
@@ -10027,8 +10028,8 @@
       <c r="A141" t="s">
         <v>223</v>
       </c>
-      <c r="B141" t="s">
-        <v>349</v>
+      <c r="B141" s="13">
+        <v>3.33</v>
       </c>
       <c r="C141" t="s">
         <v>3</v>
@@ -10047,8 +10048,8 @@
       <c r="A142" t="s">
         <v>224</v>
       </c>
-      <c r="B142" t="s">
-        <v>349</v>
+      <c r="B142" s="13">
+        <v>3.33</v>
       </c>
       <c r="C142" t="s">
         <v>3</v>
@@ -10067,8 +10068,8 @@
       <c r="A143" t="s">
         <v>225</v>
       </c>
-      <c r="B143" t="s">
-        <v>349</v>
+      <c r="B143" s="13">
+        <v>3.33</v>
       </c>
       <c r="C143" t="s">
         <v>3</v>
@@ -10087,8 +10088,8 @@
       <c r="A144" t="s">
         <v>226</v>
       </c>
-      <c r="B144" t="s">
-        <v>349</v>
+      <c r="B144" s="13">
+        <v>3.33</v>
       </c>
       <c r="C144" t="s">
         <v>3</v>
@@ -10107,8 +10108,8 @@
       <c r="A145" t="s">
         <v>227</v>
       </c>
-      <c r="B145" t="s">
-        <v>349</v>
+      <c r="B145" s="13">
+        <v>3.33</v>
       </c>
       <c r="C145" t="s">
         <v>3</v>
@@ -10127,8 +10128,8 @@
       <c r="A146" t="s">
         <v>228</v>
       </c>
-      <c r="B146" t="s">
-        <v>349</v>
+      <c r="B146" s="13">
+        <v>3.33</v>
       </c>
       <c r="C146" t="s">
         <v>3</v>
@@ -10147,8 +10148,8 @@
       <c r="A147" t="s">
         <v>229</v>
       </c>
-      <c r="B147" t="s">
-        <v>3</v>
+      <c r="B147" s="13">
+        <v>0</v>
       </c>
       <c r="C147" t="s">
         <v>3</v>
@@ -10167,8 +10168,8 @@
       <c r="A148" t="s">
         <v>230</v>
       </c>
-      <c r="B148" t="s">
-        <v>3</v>
+      <c r="B148" s="13">
+        <v>0</v>
       </c>
       <c r="C148" t="s">
         <v>3</v>
@@ -10187,8 +10188,8 @@
       <c r="A149" t="s">
         <v>231</v>
       </c>
-      <c r="B149" t="s">
-        <v>3</v>
+      <c r="B149" s="13">
+        <v>0</v>
       </c>
       <c r="C149" t="s">
         <v>3</v>
@@ -10207,8 +10208,8 @@
       <c r="A150" t="s">
         <v>232</v>
       </c>
-      <c r="B150" t="s">
-        <v>349</v>
+      <c r="B150" s="13">
+        <v>3.33</v>
       </c>
       <c r="C150" t="s">
         <v>3</v>
@@ -10227,8 +10228,8 @@
       <c r="A151" t="s">
         <v>233</v>
       </c>
-      <c r="B151" t="s">
-        <v>349</v>
+      <c r="B151" s="13">
+        <v>3.33</v>
       </c>
       <c r="C151" t="s">
         <v>3</v>
@@ -10247,8 +10248,8 @@
       <c r="A152" t="s">
         <v>234</v>
       </c>
-      <c r="B152" t="s">
-        <v>349</v>
+      <c r="B152" s="13">
+        <v>3.33</v>
       </c>
       <c r="C152" t="s">
         <v>3</v>
@@ -10267,8 +10268,8 @@
       <c r="A153" t="s">
         <v>235</v>
       </c>
-      <c r="B153" t="s">
-        <v>3</v>
+      <c r="B153" s="13">
+        <v>0</v>
       </c>
       <c r="C153" t="s">
         <v>3</v>
@@ -10287,8 +10288,8 @@
       <c r="A154" t="s">
         <v>236</v>
       </c>
-      <c r="B154" t="s">
-        <v>3</v>
+      <c r="B154" s="13">
+        <v>0</v>
       </c>
       <c r="C154" t="s">
         <v>3</v>
@@ -10307,8 +10308,8 @@
       <c r="A155" t="s">
         <v>237</v>
       </c>
-      <c r="B155" t="s">
-        <v>3</v>
+      <c r="B155" s="13">
+        <v>0</v>
       </c>
       <c r="C155" t="s">
         <v>3</v>
@@ -10327,8 +10328,8 @@
       <c r="A156" t="s">
         <v>238</v>
       </c>
-      <c r="B156" t="s">
-        <v>349</v>
+      <c r="B156" s="13">
+        <v>3.33</v>
       </c>
       <c r="C156" t="s">
         <v>3</v>
@@ -10347,8 +10348,8 @@
       <c r="A157" t="s">
         <v>239</v>
       </c>
-      <c r="B157" t="s">
-        <v>349</v>
+      <c r="B157" s="13">
+        <v>3.33</v>
       </c>
       <c r="C157" t="s">
         <v>3</v>
@@ -10367,8 +10368,8 @@
       <c r="A158" t="s">
         <v>240</v>
       </c>
-      <c r="B158" t="s">
-        <v>349</v>
+      <c r="B158" s="13">
+        <v>3.33</v>
       </c>
       <c r="C158" t="s">
         <v>3</v>
@@ -10387,8 +10388,8 @@
       <c r="A159" t="s">
         <v>241</v>
       </c>
-      <c r="B159" t="s">
-        <v>3</v>
+      <c r="B159" s="13">
+        <v>0</v>
       </c>
       <c r="C159" t="s">
         <v>3</v>
@@ -10407,8 +10408,8 @@
       <c r="A160" t="s">
         <v>242</v>
       </c>
-      <c r="B160" t="s">
-        <v>3</v>
+      <c r="B160" s="13">
+        <v>0</v>
       </c>
       <c r="C160" t="s">
         <v>3</v>
@@ -10427,8 +10428,8 @@
       <c r="A161" t="s">
         <v>243</v>
       </c>
-      <c r="B161" t="s">
-        <v>350</v>
+      <c r="B161" s="13">
+        <v>3.68</v>
       </c>
       <c r="C161" t="s">
         <v>3</v>
@@ -10447,8 +10448,8 @@
       <c r="A162" t="s">
         <v>244</v>
       </c>
-      <c r="B162" t="s">
-        <v>3</v>
+      <c r="B162" s="13">
+        <v>0</v>
       </c>
       <c r="C162" t="s">
         <v>3</v>
@@ -10467,8 +10468,8 @@
       <c r="A163" t="s">
         <v>245</v>
       </c>
-      <c r="B163" t="s">
-        <v>3</v>
+      <c r="B163" s="13">
+        <v>0</v>
       </c>
       <c r="C163" t="s">
         <v>3</v>
@@ -10487,8 +10488,8 @@
       <c r="A164" t="s">
         <v>246</v>
       </c>
-      <c r="B164" t="s">
-        <v>3</v>
+      <c r="B164" s="13">
+        <v>0</v>
       </c>
       <c r="C164" t="s">
         <v>3</v>
@@ -10507,8 +10508,8 @@
       <c r="A165" t="s">
         <v>247</v>
       </c>
-      <c r="B165" t="s">
-        <v>349</v>
+      <c r="B165" s="13">
+        <v>3.33</v>
       </c>
       <c r="C165" t="s">
         <v>3</v>
@@ -10527,8 +10528,8 @@
       <c r="A166" t="s">
         <v>248</v>
       </c>
-      <c r="B166" t="s">
-        <v>349</v>
+      <c r="B166" s="13">
+        <v>3.33</v>
       </c>
       <c r="C166" t="s">
         <v>3</v>
@@ -10547,8 +10548,8 @@
       <c r="A167" t="s">
         <v>249</v>
       </c>
-      <c r="B167" t="s">
-        <v>349</v>
+      <c r="B167" s="13">
+        <v>3.33</v>
       </c>
       <c r="C167" t="s">
         <v>3</v>
@@ -10561,6 +10562,12 @@
       </c>
       <c r="F167" t="s">
         <v>569</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B169">
+        <f>SUM(B3:B167)</f>
+        <v>268.15000000000038</v>
       </c>
     </row>
   </sheetData>
